--- a/experiments/light_snow_experiments.xlsx
+++ b/experiments/light_snow_experiments.xlsx
@@ -241,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LightSnowExperiments" displayName="LightSnowExperiments" ref="A1:L9" totalsRowShown="0">
-  <autoFilter ref="A1:L9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LightSnowExperiments" displayName="LightSnowExperiments" ref="A1:L25" totalsRowShown="0">
+  <autoFilter ref="A1:L25">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -276,7 +276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -346,12 +346,12 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>39.2171</t>
+          <t>33.1257</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>32.0921</t>
+          <t>26.7948</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -366,12 +366,12 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>-5.0191</t>
+          <t>1.0723</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>-4.8905</t>
+          <t>0.4068</t>
         </is>
       </c>
     </row>
@@ -396,12 +396,12 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>25.7518</t>
+          <t>25.9751</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>17.8163</t>
+          <t>17.3826</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -416,12 +416,12 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>0.9072</t>
+          <t>0.6839</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>1.3248</t>
+          <t>1.7585</t>
         </is>
       </c>
     </row>
@@ -446,12 +446,12 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>64.7247</t>
+          <t>63.8172</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>60.9319</t>
+          <t>58.8241</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -466,12 +466,12 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2.3874</t>
+          <t>3.2949</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>-2.9413</t>
+          <t>-0.8335</t>
         </is>
       </c>
     </row>
@@ -496,12 +496,12 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>5.7045</t>
+          <t>6.8837</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>5.6691</t>
+          <t>6.6531</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>13.8468</t>
+          <t>12.6676</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>13.8207</t>
+          <t>12.8367</t>
         </is>
       </c>
     </row>
@@ -546,12 +546,12 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>34.5645</t>
+          <t>37.0115</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>27.6794</t>
+          <t>28.6313</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -566,12 +566,12 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>-1.4859</t>
+          <t>-3.9329</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>-0.0332</t>
+          <t>-0.9851</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>26.9327</t>
+          <t>23.1462</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>18.4261</t>
+          <t>16.2547</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -616,12 +616,12 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>-0.3277</t>
+          <t>3.4588</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>1.6228</t>
+          <t>3.7942</t>
         </is>
       </c>
     </row>
@@ -646,12 +646,12 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>60.6975</t>
+          <t>64.9745</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>58.2509</t>
+          <t>59.8047</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>-1.0179</t>
+          <t>-5.2949</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>-6.5232</t>
+          <t>-8.0770</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>3.3338</t>
+          <t>5.1496</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>3.2315</t>
+          <t>5.0739</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -716,61 +716,925 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>15.0774</t>
+          <t>13.2616</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>15.1688</t>
+          <t>13.3264</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>average(8)</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="s">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>group10</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>36.8416</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>30.1664</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>35.8885</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>29.2075</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>-0.9531</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>-0.9589</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>group11</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>25.1855</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>16.7085</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>25.8657</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>19.5473</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>0.6802</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>2.8388</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>group12</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>66.1390</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>62.1039</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>62.5806</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>52.3610</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>-3.5584</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>-9.7429</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>group13</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>3.7845</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>3.6291</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>11.8952</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>11.8110</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>8.1107</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>8.1819</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>group14</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>37.8400</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>30.8861</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>36.3323</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>29.9104</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>-1.5077</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>-0.9757</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>group15</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>26.4919</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>18.3685</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>26.9572</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>19.9213</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>0.4653</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>1.5528</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>group16</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>53.2109</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>49.2509</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>60.7050</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>54.1876</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>7.4941</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>4.9367</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>group17</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>1.9569</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>1.8859</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>23.4525</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>23.2106</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>21.4956</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>21.3247</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>group18</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>39.2139</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>31.8767</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>30.6210</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>24.9506</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>-8.5929</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>-6.9261</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>group19</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>24.4324</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>17.1809</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>24.1088</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>17.2482</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>-0.3236</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>0.0673</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>group20</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>70.0386</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>63.9042</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>69.8543</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>54.4855</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>-0.1843</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>-9.4187</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>group21</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>4.8797</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>4.7713</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>20.4054</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>19.8644</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>15.5257</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>15.0931</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>group22</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>37.4594</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>29.8119</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>26.2118</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>21.0771</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>-11.2476</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>-8.7348</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>group23</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>22.7480</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>14.4542</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>27.0213</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>19.6912</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>4.2733</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>5.2370</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>group24</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>66.8676</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>61.5301</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>62.6686</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>50.8375</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>-4.1990</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>-10.6926</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>group25</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>1.9022</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>1.6321</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>22.9440</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>20.4083</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>21.0418</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>18.7762</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>average(24)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>3.0460</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>2.1936</t>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>3.0721</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>2.1994</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L9"/>
+  <autoFilter ref="A1:L25"/>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <tableParts count="1">
